--- a/MULTIPUNTO/6372 Datos Multipunto METALURGICAS MARTINEZ.xlsx
+++ b/MULTIPUNTO/6372 Datos Multipunto METALURGICAS MARTINEZ.xlsx
@@ -17,8 +17,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="DD/MM/YYYY"/>
+    <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -49,9 +49,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,21 +418,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P25"/>
+  <dimension ref="A1:P31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
-    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
-    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
     <col width="8" customWidth="1" min="13" max="13"/>
     <col width="8" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
@@ -526,17 +527,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CE ENERGÍA, S.A.</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="D2" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="E2" s="1" t="n">
-        <v>46210</v>
+          <t>ELEIA</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>46209</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>46213</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -544,13 +545,13 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.228378</v>
+        <v>0.2321903057702504</v>
       </c>
       <c r="H2" t="n">
-        <v>0.140409</v>
+        <v>0.1552908559785571</v>
       </c>
       <c r="I2" t="n">
-        <v>0.112008</v>
+        <v>0.1279152338959516</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -584,17 +585,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CE ENERGÍA, S.A.</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>46210</v>
+          <t>ELEIA</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>46209</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>46213</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -602,37 +603,37 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.20376</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.161756</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0.132449</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0.107673</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0.088375</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0.112552</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>0.967</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>3.0TD</t>
+          <t>2.0TD</t>
         </is>
       </c>
     </row>
@@ -642,17 +643,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CE ENERGÍA, S.A.</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46210</v>
+          <t>ELEIA</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>46209</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>46213</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -660,22 +661,22 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.172734</v>
+        <v>0.2126769468809737</v>
       </c>
       <c r="H4" t="n">
-        <v>0.139564</v>
+        <v>0.1762301249094594</v>
       </c>
       <c r="I4" t="n">
-        <v>0.118576</v>
+        <v>0.1404260806094815</v>
       </c>
       <c r="J4" t="n">
-        <v>0.09761400000000001</v>
+        <v>0.1213799725894571</v>
       </c>
       <c r="K4" t="n">
-        <v>0.079376</v>
+        <v>0.1044094080005359</v>
       </c>
       <c r="L4" t="n">
-        <v>0.104357</v>
+        <v>0.1248900054357413</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -690,7 +691,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>6.1TD</t>
+          <t>3.0TD</t>
         </is>
       </c>
     </row>
@@ -703,14 +704,14 @@
           <t>ELEIA</t>
         </is>
       </c>
-      <c r="C5" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46210</v>
+      <c r="C5" s="2" t="n">
+        <v>46209</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>46213</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -718,13 +719,13 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.2321903057702504</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1552908559785571</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1279152338959516</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -736,19 +737,19 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>0.967</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2.0TD</t>
+          <t>3.0TD</t>
         </is>
       </c>
     </row>
@@ -761,14 +762,14 @@
           <t>ELEIA</t>
         </is>
       </c>
-      <c r="C6" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46210</v>
+      <c r="C6" s="2" t="n">
+        <v>46209</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>46213</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -776,37 +777,37 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>0.1836611677593081</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.1523879495943681</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.1245462933828552</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>0.1106890387083001</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.09721287955475288</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.1161136137793446</v>
       </c>
       <c r="M6" t="n">
-        <v>0.967</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2.0TD</t>
+          <t>6.1TD</t>
         </is>
       </c>
     </row>
@@ -819,14 +820,14 @@
           <t>ELEIA</t>
         </is>
       </c>
-      <c r="C7" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46210</v>
+      <c r="C7" s="2" t="n">
+        <v>46209</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>46213</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -834,37 +835,37 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.2126769468809737</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1762301249094594</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1404260806094815</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1213799725894571</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1044094080005359</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1248900054357413</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>0.967</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>3.0TD</t>
+          <t>6.1TD</t>
         </is>
       </c>
     </row>
@@ -874,17 +875,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ELEIA</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="n">
+          <t>ENERGYA VM</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
         <v>46210</v>
       </c>
-      <c r="D8" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46210</v>
+      <c r="D8" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>46213</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -892,13 +893,13 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>0.225418</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>0.144702</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.11562</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -910,19 +911,19 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.967</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>3.0TD</t>
+          <t>2.0TD</t>
         </is>
       </c>
     </row>
@@ -932,17 +933,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ELEIA</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="n">
+          <t>ENERGYA VM</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
         <v>46210</v>
       </c>
-      <c r="D9" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46210</v>
+      <c r="D9" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>46213</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -950,37 +951,37 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.1836611677593081</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1523879495943681</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1245462933828552</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1106890387083001</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.09721287955475288</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1161136137793446</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>6.1TD</t>
+          <t>2.0TD</t>
         </is>
       </c>
     </row>
@@ -990,17 +991,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ELEIA</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="n">
+          <t>ENERGYA VM</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
         <v>46210</v>
       </c>
-      <c r="D10" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46210</v>
+      <c r="D10" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>46213</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1008,37 +1009,37 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>0.186692</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>0.156747</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>0.130507</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>0.109694</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>0.09471400000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>0.110292</v>
       </c>
       <c r="M10" t="n">
-        <v>0.967</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>6.1TD</t>
+          <t>3.0TD</t>
         </is>
       </c>
     </row>
@@ -1051,14 +1052,14 @@
           <t>ENERGYA VM</t>
         </is>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>46210</v>
       </c>
-      <c r="D11" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46210</v>
+      <c r="D11" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>46213</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1066,13 +1067,13 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0.225418</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0.144702</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0.11562</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1084,19 +1085,19 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2.0TD</t>
+          <t>3.0TD</t>
         </is>
       </c>
     </row>
@@ -1109,14 +1110,14 @@
           <t>ENERGYA VM</t>
         </is>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>46210</v>
       </c>
-      <c r="D12" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46210</v>
+      <c r="D12" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>46213</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1124,22 +1125,22 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0.186692</v>
+        <v>0.15177</v>
       </c>
       <c r="H12" t="n">
-        <v>0.156747</v>
+        <v>0.129799</v>
       </c>
       <c r="I12" t="n">
-        <v>0.130507</v>
+        <v>0.108713</v>
       </c>
       <c r="J12" t="n">
-        <v>0.109694</v>
+        <v>0.092294</v>
       </c>
       <c r="K12" t="n">
-        <v>0.09471400000000001</v>
+        <v>0.08339100000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>0.110292</v>
+        <v>0.100642</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1154,7 +1155,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>3.0TD</t>
+          <t>6.1TD</t>
         </is>
       </c>
     </row>
@@ -1167,14 +1168,14 @@
           <t>ENERGYA VM</t>
         </is>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>46210</v>
       </c>
-      <c r="D13" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46210</v>
+      <c r="D13" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>46213</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1182,32 +1183,32 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.15177</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0.129799</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0.108713</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0.092294</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.08339100000000001</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0.100642</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1225,14 +1226,14 @@
           <t>IBERDROLA</t>
         </is>
       </c>
-      <c r="C14" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46210</v>
+      <c r="C14" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>46213</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1283,14 +1284,14 @@
           <t>IBERDROLA</t>
         </is>
       </c>
-      <c r="C15" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46210</v>
+      <c r="C15" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>46213</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1341,14 +1342,14 @@
           <t>IBERDROLA</t>
         </is>
       </c>
-      <c r="C16" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46210</v>
+      <c r="C16" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>46213</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1399,14 +1400,14 @@
           <t>IBERDROLA</t>
         </is>
       </c>
-      <c r="C17" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46210</v>
+      <c r="C17" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>46213</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1457,14 +1458,14 @@
           <t>IBERDROLA</t>
         </is>
       </c>
-      <c r="C18" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46210</v>
+      <c r="C18" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>46213</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1515,14 +1516,14 @@
           <t>IBERDROLA</t>
         </is>
       </c>
-      <c r="C19" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46210</v>
+      <c r="C19" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>46213</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1573,14 +1574,14 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C20" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46210</v>
+      <c r="C20" s="2" t="n">
+        <v>46209</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>46213</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1631,14 +1632,14 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C21" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46210</v>
+      <c r="C21" s="2" t="n">
+        <v>46209</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>46213</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1689,14 +1690,14 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C22" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46210</v>
+      <c r="C22" s="2" t="n">
+        <v>46209</v>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>46213</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1747,14 +1748,14 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C23" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46210</v>
+      <c r="C23" s="2" t="n">
+        <v>46209</v>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>46213</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1805,14 +1806,14 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C24" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46210</v>
+      <c r="C24" s="2" t="n">
+        <v>46209</v>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>46213</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1863,14 +1864,14 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C25" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46210</v>
+      <c r="C25" s="2" t="n">
+        <v>46209</v>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>46213</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1907,6 +1908,354 @@
         </is>
       </c>
       <c r="P25" t="inlineStr">
+        <is>
+          <t>6.1TD</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>6372</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>VISALIA</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>46210</v>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>46213</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>0.228378</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.140409</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.112008</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>2.0TD</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>6372</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>VISALIA</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>46210</v>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>46213</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>0.20376</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.161756</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.132449</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.107673</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.088375</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.112552</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>3.0TD</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>6372</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>VISALIA</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>46210</v>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>46213</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>0.172734</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.139564</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.118576</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.09761400000000001</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.079376</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.104357</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>6.1TD</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>6372</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>AUDAX</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>46212</v>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>46213</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>0.1279</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.1279</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.1279</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>2.0TD</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>6372</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>AUDAX</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>46212</v>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>46213</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>0.1337</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.1337</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.1337</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.1337</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.1337</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.1337</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>3.0TD</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>6372</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>AUDAX</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>46212</v>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>46213</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
         <is>
           <t>6.1TD</t>
         </is>

--- a/MULTIPUNTO/6372 Datos Multipunto METALURGICAS MARTINEZ.xlsx
+++ b/MULTIPUNTO/6372 Datos Multipunto METALURGICAS MARTINEZ.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P31"/>
+  <dimension ref="A1:P37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -427,9 +427,9 @@
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
@@ -2261,6 +2261,354 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>6372</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>NEXUS</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>46212</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>46213</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>0.24182</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.163053</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.130629</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>2.0TD</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>6372</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>NEXUS</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>46212</v>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>46213</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="N33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>2.0TD</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>6372</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>NEXUS</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>46212</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>46213</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>0.215785</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.183585</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.14633</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.121653</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.105064</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.125185</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>3.0TD</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>6372</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>NEXUS</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>46212</v>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>46213</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>3.0TD</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>6372</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>NEXUS</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>46212</v>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>46213</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>0.186691</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.158875</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.130392</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.110464</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.09431300000000001</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.112991</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>6.1TD</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>6372</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>NEXUS</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>46212</v>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>46213</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="N37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>6.1TD</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
